--- a/docs/Decodifiche/2_dec_tipo_contenuto.xlsx
+++ b/docs/Decodifiche/2_dec_tipo_contenuto.xlsx
@@ -68,7 +68,7 @@
     <t>RIFIUTO</t>
   </si>
   <si>
-    <t>2024-05-29 00:00:00.0</t>
+    <t>2024-05-30 00:00:00.0</t>
   </si>
 </sst>
 </file>
